--- a/web/files/港岛-半山区西部-Upper Central.xlsx
+++ b/web/files/港岛-半山区西部-Upper Central.xlsx
@@ -1268,7 +1268,7 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="H11" s="5" t="n">
@@ -1454,7 +1454,7 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="H14" s="5" t="n">
@@ -1516,7 +1516,7 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>2025-12-14</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="H15" s="5" t="n">
@@ -1640,7 +1640,7 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="H17" s="5" t="n">
@@ -1702,7 +1702,7 @@
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="H18" s="5" t="n">
@@ -1764,7 +1764,7 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="H19" s="5" t="n">
@@ -1888,7 +1888,7 @@
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>2025-12-21</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="H21" s="5" t="n">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>2025-05-14</t>
+          <t>2025-05-15</t>
         </is>
       </c>
       <c r="H22" s="5" t="n">
@@ -2012,7 +2012,7 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="H23" s="5" t="n">
@@ -2074,7 +2074,7 @@
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="H24" s="5" t="n">
@@ -2136,7 +2136,7 @@
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="H25" s="5" t="n">
@@ -2198,7 +2198,7 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>2025-03-27</t>
+          <t>2025-03-28</t>
         </is>
       </c>
       <c r="H26" s="5" t="n">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="H27" s="5" t="n">
@@ -2322,7 +2322,7 @@
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="H28" s="5" t="n">
@@ -2384,7 +2384,7 @@
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="H29" s="5" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>2025-03-03</t>
+          <t>2025-03-04</t>
         </is>
       </c>
       <c r="H30" s="5" t="n">
@@ -2508,7 +2508,7 @@
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="H31" s="5" t="n">
@@ -2570,7 +2570,7 @@
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>2025-01-13</t>
+          <t>2025-01-14</t>
         </is>
       </c>
       <c r="H32" s="5" t="n">
@@ -2632,7 +2632,7 @@
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="H33" s="5" t="n">
@@ -2694,7 +2694,7 @@
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="H34" s="5" t="n">
@@ -2756,7 +2756,7 @@
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="H35" s="5" t="n">
@@ -2818,7 +2818,7 @@
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="H36" s="5" t="n">
@@ -2880,7 +2880,7 @@
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="H37" s="5" t="n">
@@ -2942,7 +2942,7 @@
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>2025-02-20</t>
+          <t>2025-02-21</t>
         </is>
       </c>
       <c r="H38" s="5" t="n">
@@ -3004,7 +3004,7 @@
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="H39" s="5" t="n">
@@ -3066,7 +3066,7 @@
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="H40" s="5" t="n">
@@ -3128,7 +3128,7 @@
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="H41" s="5" t="n">
@@ -3190,7 +3190,7 @@
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="H42" s="5" t="n">
@@ -3252,7 +3252,7 @@
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="H43" s="5" t="n">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="H44" s="5" t="n">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="H45" s="5" t="n">
@@ -3438,7 +3438,7 @@
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>2024-11-04</t>
+          <t>2024-11-05</t>
         </is>
       </c>
       <c r="H46" s="5" t="n">
@@ -3500,7 +3500,7 @@
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="H47" s="5" t="n">
@@ -3562,7 +3562,7 @@
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="H48" s="5" t="n">
@@ -3624,7 +3624,7 @@
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="H49" s="5" t="n">
@@ -3686,7 +3686,7 @@
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="H50" s="5" t="n">
@@ -3748,7 +3748,7 @@
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="H51" s="5" t="n">
@@ -3810,7 +3810,7 @@
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>2025-12-21</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="H52" s="5" t="n">
@@ -3872,7 +3872,7 @@
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="H53" s="5" t="n">
@@ -3934,7 +3934,7 @@
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>2024-10-27</t>
+          <t>2024-10-28</t>
         </is>
       </c>
       <c r="H54" s="5" t="n">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="H55" s="5" t="n">
@@ -4058,7 +4058,7 @@
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="H56" s="5" t="n">
@@ -4120,7 +4120,7 @@
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="H57" s="5" t="n">
@@ -4182,7 +4182,7 @@
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="H58" s="5" t="n">
@@ -4244,7 +4244,7 @@
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="H59" s="5" t="n">
@@ -4306,7 +4306,7 @@
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="H60" s="5" t="n">
@@ -4368,7 +4368,7 @@
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="H61" s="5" t="n">
@@ -4430,7 +4430,7 @@
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-10-16</t>
         </is>
       </c>
       <c r="H62" s="5" t="n">
@@ -4492,7 +4492,7 @@
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="H63" s="5" t="n">
@@ -4554,7 +4554,7 @@
       </c>
       <c r="G64" s="3" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="H64" s="5" t="n">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="H65" s="5" t="n">
@@ -4678,7 +4678,7 @@
       </c>
       <c r="G66" s="3" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="H66" s="5" t="n">
@@ -4740,7 +4740,7 @@
       </c>
       <c r="G67" s="3" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="H67" s="5" t="n">
@@ -4802,7 +4802,7 @@
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>2025-06-12</t>
+          <t>2025-06-13</t>
         </is>
       </c>
       <c r="H68" s="5" t="n">
@@ -4864,7 +4864,7 @@
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-12-19</t>
         </is>
       </c>
       <c r="H69" s="5" t="n">
@@ -4926,7 +4926,7 @@
       </c>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t>2025-12-21</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="H70" s="5" t="n">
@@ -4988,7 +4988,7 @@
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
-          <t>2025-12-21</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="H71" s="5" t="n">
@@ -5050,7 +5050,7 @@
       </c>
       <c r="G72" s="3" t="inlineStr">
         <is>
-          <t>2026-02-08</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="H72" s="5" t="n">
@@ -5112,7 +5112,7 @@
       </c>
       <c r="G73" s="3" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="H73" s="5" t="n">
@@ -5174,7 +5174,7 @@
       </c>
       <c r="G74" s="3" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="H74" s="5" t="n">
@@ -5236,7 +5236,7 @@
       </c>
       <c r="G75" s="3" t="inlineStr">
         <is>
-          <t>2024-12-17</t>
+          <t>2024-12-18</t>
         </is>
       </c>
       <c r="H75" s="5" t="n">
@@ -5298,7 +5298,7 @@
       </c>
       <c r="G76" s="3" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="H76" s="5" t="n">
@@ -5360,7 +5360,7 @@
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="H77" s="5" t="n">
@@ -5422,7 +5422,7 @@
       </c>
       <c r="G78" s="3" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-12-19</t>
         </is>
       </c>
       <c r="H78" s="5" t="n">
@@ -5484,7 +5484,7 @@
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="H79" s="5" t="n">
@@ -5546,7 +5546,7 @@
       </c>
       <c r="G80" s="3" t="inlineStr">
         <is>
-          <t>2025-07-13</t>
+          <t>2025-07-14</t>
         </is>
       </c>
       <c r="H80" s="5" t="n">
@@ -5608,7 +5608,7 @@
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="H81" s="5" t="n">
@@ -5670,7 +5670,7 @@
       </c>
       <c r="G82" s="3" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="H82" s="5" t="n">
@@ -5732,7 +5732,7 @@
       </c>
       <c r="G83" s="3" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="H83" s="5" t="n">
@@ -5794,7 +5794,7 @@
       </c>
       <c r="G84" s="3" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-19</t>
         </is>
       </c>
       <c r="H84" s="5" t="n">
@@ -5856,7 +5856,7 @@
       </c>
       <c r="G85" s="3" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-12-19</t>
         </is>
       </c>
       <c r="H85" s="5" t="n">
@@ -5918,7 +5918,7 @@
       </c>
       <c r="G86" s="3" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="H86" s="5" t="n">
@@ -5980,7 +5980,7 @@
       </c>
       <c r="G87" s="3" t="inlineStr">
         <is>
-          <t>2025-03-30</t>
+          <t>2025-03-31</t>
         </is>
       </c>
       <c r="H87" s="5" t="n">
@@ -6249,7 +6249,7 @@
           <t>E | 389呎 (2房)
 $1257万
 $32,303/呎
-(26年-03月-31日)</t>
+(26年-04月-01日)</t>
         </is>
       </c>
     </row>
@@ -6274,7 +6274,7 @@
           <t>D | 244呎 (开放式)
 $698万
 $28,623/呎
-(25年-12月-14日)</t>
+(25年-12月-15日)</t>
         </is>
       </c>
       <c r="F8" s="23" t="inlineStr">
@@ -6282,7 +6282,7 @@
           <t>E | 389呎 (2房)
 $1181万
 $30,357/呎
-(25年-12月-10日)</t>
+(25年-12月-11日)</t>
         </is>
       </c>
     </row>
@@ -6297,7 +6297,7 @@
           <t>A | 197呎 (开放式)
 $626万
 $31,797/呎
-(26年-07月-15日)</t>
+(26年-07月-16日)</t>
         </is>
       </c>
       <c r="C9" s="21" t="inlineStr"/>
@@ -6307,7 +6307,7 @@
           <t>D | 244呎 (开放式)
 $692万
 $28,365/呎
-(26年-03月-24日)</t>
+(26年-03月-25日)</t>
         </is>
       </c>
       <c r="F9" s="23" t="inlineStr">
@@ -6315,7 +6315,7 @@
           <t>E | 389呎 (2房)
 $1170万
 $30,087/呎
-(26年-02月-02日)</t>
+(26年-02月-03日)</t>
         </is>
       </c>
     </row>
@@ -6330,7 +6330,7 @@
           <t>A | 196呎 (开放式)
 $589万
 $30,036/呎
-(26年-06月-16日)</t>
+(26年-06月-17日)</t>
         </is>
       </c>
       <c r="C10" s="23" t="inlineStr">
@@ -6338,7 +6338,7 @@
           <t>B | 168呎 (开放式)
 $470万
 $28,000/呎
-(25年-05月-14日)</t>
+(25年-05月-15日)</t>
         </is>
       </c>
       <c r="D10" s="23" t="inlineStr">
@@ -6346,7 +6346,7 @@
           <t>C | 241呎 (开放式)
 $678万
 $28,112/呎
-(25年-12月-21日)</t>
+(25年-12月-22日)</t>
         </is>
       </c>
       <c r="E10" s="22" t="inlineStr">
@@ -6370,7 +6370,7 @@
           <t>A | 196呎 (开放式)
 $563万
 $28,714/呎
-(26年-05月-27日)</t>
+(26年-05月-28日)</t>
         </is>
       </c>
       <c r="C11" s="23" t="inlineStr">
@@ -6378,7 +6378,7 @@
           <t>B | 168呎 (开放式)
 $436万
 $25,946/呎
-(25年-03月-27日)</t>
+(25年-03月-28日)</t>
         </is>
       </c>
       <c r="D11" s="23" t="inlineStr">
@@ -6386,7 +6386,7 @@
           <t>C | 241呎 (开放式)
 $661万
 $27,411/呎
-(26年-05月-10日)</t>
+(26年-05月-11日)</t>
         </is>
       </c>
       <c r="E11" s="23" t="inlineStr">
@@ -6394,7 +6394,7 @@
           <t>D | 244呎 (开放式)
 $689万
 $28,238/呎
-(26年-07月-14日)</t>
+(26年-07月-15日)</t>
         </is>
       </c>
       <c r="F11" s="21" t="inlineStr"/>
@@ -6410,7 +6410,7 @@
           <t>A | 196呎 (开放式)
 $515万
 $26,296/呎
-(25年-12月-11日)</t>
+(25年-12月-12日)</t>
         </is>
       </c>
       <c r="C12" s="23" t="inlineStr">
@@ -6418,7 +6418,7 @@
           <t>B | 168呎 (开放式)
 $432万
 $25,690/呎
-(25年-03月-03日)</t>
+(25年-03月-04日)</t>
         </is>
       </c>
       <c r="D12" s="23" t="inlineStr">
@@ -6426,7 +6426,7 @@
           <t>C | 241呎 (开放式)
 $674万
 $27,963/呎
-(26年-07月-15日)</t>
+(26年-07月-16日)</t>
         </is>
       </c>
       <c r="E12" s="23" t="inlineStr">
@@ -6434,7 +6434,7 @@
           <t>D | 244呎 (开放式)
 $662万
 $27,148/呎
-(26年-05月-19日)</t>
+(26年-05月-20日)</t>
         </is>
       </c>
       <c r="F12" s="21" t="inlineStr"/>
@@ -6450,7 +6450,7 @@
           <t>A | 196呎 (开放式)
 $536万
 $27,347/呎
-(26年-05月-19日)</t>
+(26年-05月-20日)</t>
         </is>
       </c>
       <c r="C13" s="23" t="inlineStr">
@@ -6458,7 +6458,7 @@
           <t>B | 168呎 (开放式)
 $462万
 $27,518/呎
-(26年-02月-12日)</t>
+(26年-02月-13日)</t>
         </is>
       </c>
       <c r="D13" s="23" t="inlineStr">
@@ -6466,7 +6466,7 @@
           <t>C | 241呎 (开放式)
 $617万
 $25,606/呎
-(25年-12月-08日)</t>
+(25年-12月-09日)</t>
         </is>
       </c>
       <c r="E13" s="23" t="inlineStr">
@@ -6474,7 +6474,7 @@
           <t>D | 244呎 (开放式)
 $625万
 $25,611/呎
-(25年-01月-13日)</t>
+(25年-01月-14日)</t>
         </is>
       </c>
       <c r="F13" s="21" t="inlineStr"/>
@@ -6490,7 +6490,7 @@
           <t>A | 196呎 (开放式)
 $516万
 $26,316/呎
-(26年-01月-21日)</t>
+(26年-01月-22日)</t>
         </is>
       </c>
       <c r="C14" s="23" t="inlineStr">
@@ -6498,7 +6498,7 @@
           <t>B | 168呎 (开放式)
 $423万
 $25,190/呎
-(25年-02月-20日)</t>
+(25年-02月-21日)</t>
         </is>
       </c>
       <c r="D14" s="23" t="inlineStr">
@@ -6506,7 +6506,7 @@
           <t>C | 241呎 (开放式)
 $611万
 $25,365/呎
-(25年-12月-03日)</t>
+(25年-12月-04日)</t>
         </is>
       </c>
       <c r="E14" s="23" t="inlineStr">
@@ -6514,7 +6514,7 @@
           <t>D | 244呎 (开放式)
 $644万
 $26,381/呎
-(26年-05月-07日)</t>
+(26年-05月-08日)</t>
         </is>
       </c>
       <c r="F14" s="21" t="inlineStr"/>
@@ -6530,7 +6530,7 @@
           <t>A | 196呎 (开放式)
 $501万
 $25,556/呎
-(25年-11月-26日)</t>
+(25年-11月-27日)</t>
         </is>
       </c>
       <c r="C15" s="23" t="inlineStr">
@@ -6538,7 +6538,7 @@
           <t>B | 168呎 (开放式)
 $440万
 $26,196/呎
-(25年-12月-17日)</t>
+(25年-12月-18日)</t>
         </is>
       </c>
       <c r="D15" s="23" t="inlineStr">
@@ -6546,7 +6546,7 @@
           <t>C | 241呎 (开放式)
 $605万
 $25,120/呎
-(25年-12月-01日)</t>
+(25年-12月-02日)</t>
         </is>
       </c>
       <c r="E15" s="23" t="inlineStr">
@@ -6554,7 +6554,7 @@
           <t>D | 244呎 (开放式)
 $638万
 $26,127/呎
-(26年-03月-26日)</t>
+(26年-03月-27日)</t>
         </is>
       </c>
       <c r="F15" s="21" t="inlineStr"/>
@@ -6570,7 +6570,7 @@
           <t>A | 196呎 (开放式)
 $508万
 $25,944/呎
-(26年-01月-20日)</t>
+(26年-01月-21日)</t>
         </is>
       </c>
       <c r="C16" s="23" t="inlineStr">
@@ -6578,7 +6578,7 @@
           <t>B | 168呎 (开放式)
 $417万
 $24,821/呎
-(24年-11月-04日)</t>
+(24年-11月-05日)</t>
         </is>
       </c>
       <c r="D16" s="23" t="inlineStr">
@@ -6586,7 +6586,7 @@
           <t>C | 241呎 (开放式)
 $627万
 $26,004/呎
-(26年-05月-28日)</t>
+(26年-05月-29日)</t>
         </is>
       </c>
       <c r="E16" s="23" t="inlineStr">
@@ -6594,7 +6594,7 @@
           <t>D | 244呎 (开放式)
 $635万
 $26,012/呎
-(26年-02月-12日)</t>
+(26年-02月-13日)</t>
         </is>
       </c>
       <c r="F16" s="21" t="inlineStr"/>
@@ -6610,7 +6610,7 @@
           <t>A | 196呎 (开放式)
 $501万
 $25,566/呎
-(26年-01月-05日)</t>
+(26年-01月-06日)</t>
         </is>
       </c>
       <c r="C17" s="23" t="inlineStr">
@@ -6618,7 +6618,7 @@
           <t>B | 168呎 (开放式)
 $444万
 $26,440/呎
-(26年-02月-10日)</t>
+(26年-02月-11日)</t>
         </is>
       </c>
       <c r="D17" s="23" t="inlineStr">
@@ -6626,7 +6626,7 @@
           <t>C | 241呎 (开放式)
 $618万
 $25,631/呎
-(26年-04月-23日)</t>
+(26年-04月-24日)</t>
         </is>
       </c>
       <c r="E17" s="23" t="inlineStr">
@@ -6634,7 +6634,7 @@
           <t>D | 244呎 (开放式)
 $601万
 $24,648/呎
-(26年-01月-26日)</t>
+(26年-01月-27日)</t>
         </is>
       </c>
       <c r="F17" s="21" t="inlineStr"/>
@@ -6650,7 +6650,7 @@
           <t>A | 196呎 (开放式)
 $487万
 $24,827/呎
-(25年-05月-26日)</t>
+(25年-05月-27日)</t>
         </is>
       </c>
       <c r="C18" s="23" t="inlineStr">
@@ -6658,7 +6658,7 @@
           <t>B | 168呎 (开放式)
 $407万
 $24,214/呎
-(24年-10月-27日)</t>
+(24年-10月-28日)</t>
         </is>
       </c>
       <c r="D18" s="23" t="inlineStr">
@@ -6666,7 +6666,7 @@
           <t>C | 241呎 (开放式)
 $588万
 $24,407/呎
-(26年-01月-26日)</t>
+(26年-01月-27日)</t>
         </is>
       </c>
       <c r="E18" s="23" t="inlineStr">
@@ -6674,7 +6674,7 @@
           <t>D | 244呎 (开放式)
 $596万
 $24,410/呎
-(25年-12月-21日)</t>
+(25年-12月-22日)</t>
         </is>
       </c>
       <c r="F18" s="21" t="inlineStr"/>
@@ -6690,7 +6690,7 @@
           <t>A | 196呎 (开放式)
 $492万
 $25,077/呎
-(25年-12月-30日)</t>
+(25年-12月-31日)</t>
         </is>
       </c>
       <c r="C19" s="23" t="inlineStr">
@@ -6698,7 +6698,7 @@
           <t>B | 168呎 (开放式)
 $436万
 $25,923/呎
-(26年-02月-11日)</t>
+(26年-02月-12日)</t>
         </is>
       </c>
       <c r="D19" s="23" t="inlineStr">
@@ -6706,7 +6706,7 @@
           <t>C | 241呎 (开放式)
 $606万
 $25,145/呎
-(26年-03月-10日)</t>
+(26年-03月-11日)</t>
         </is>
       </c>
       <c r="E19" s="23" t="inlineStr">
@@ -6714,7 +6714,7 @@
           <t>D | 244呎 (开放式)
 $590万
 $24,176/呎
-(26年-01月-06日)</t>
+(26年-01月-07日)</t>
         </is>
       </c>
       <c r="F19" s="21" t="inlineStr"/>
@@ -6730,7 +6730,7 @@
           <t>A | 196呎 (开放式)
 $506万
 $25,842/呎
-(26年-02月-10日)</t>
+(26年-02月-11日)</t>
         </is>
       </c>
       <c r="C20" s="23" t="inlineStr">
@@ -6738,7 +6738,7 @@
           <t>B | 168呎 (开放式)
 $399万
 $23,738/呎
-(24年-10月-15日)</t>
+(24年-10月-16日)</t>
         </is>
       </c>
       <c r="D20" s="23" t="inlineStr">
@@ -6746,7 +6746,7 @@
           <t>C | 241呎 (开放式)
 $600万
 $24,905/呎
-(26年-03月-16日)</t>
+(26年-03月-17日)</t>
         </is>
       </c>
       <c r="E20" s="23" t="inlineStr">
@@ -6754,7 +6754,7 @@
           <t>D | 244呎 (开放式)
 $596万
 $24,422/呎
-(26年-02月-26日)</t>
+(26年-02月-27日)</t>
         </is>
       </c>
       <c r="F20" s="21" t="inlineStr"/>
@@ -6770,7 +6770,7 @@
           <t>A | 196呎 (开放式)
 $501万
 $25,566/呎
-(26年-04月-16日)</t>
+(26年-04月-17日)</t>
         </is>
       </c>
       <c r="C21" s="23" t="inlineStr">
@@ -6778,7 +6778,7 @@
           <t>B | 168呎 (开放式)
 $427万
 $25,411/呎
-(26年-02月-01日)</t>
+(26年-02月-02日)</t>
         </is>
       </c>
       <c r="D21" s="23" t="inlineStr">
@@ -6786,7 +6786,7 @@
           <t>C | 241呎 (开放式)
 $594万
 $24,660/呎
-(26年-04月-19日)</t>
+(26年-04月-20日)</t>
         </is>
       </c>
       <c r="E21" s="23" t="inlineStr">
@@ -6794,7 +6794,7 @@
           <t>D | 244呎 (开放式)
 $602万
 $24,660/呎
-(26年-05月-06日)</t>
+(26年-05月-07日)</t>
         </is>
       </c>
       <c r="F21" s="21" t="inlineStr"/>
@@ -6810,7 +6810,7 @@
           <t>A | 196呎 (开放式)
 $478万
 $24,362/呎
-(25年-12月-21日)</t>
+(25年-12月-22日)</t>
         </is>
       </c>
       <c r="C22" s="23" t="inlineStr">
@@ -6818,7 +6818,7 @@
           <t>B | 168呎 (开放式)
 $410万
 $24,429/呎
-(25年-12月-21日)</t>
+(25年-12月-22日)</t>
         </is>
       </c>
       <c r="D22" s="23" t="inlineStr">
@@ -6826,7 +6826,7 @@
           <t>C | 241呎 (开放式)
 $566万
 $23,481/呎
-(25年-12月-18日)</t>
+(25年-12月-19日)</t>
         </is>
       </c>
       <c r="E22" s="23" t="inlineStr">
@@ -6834,7 +6834,7 @@
           <t>D | 244呎 (开放式)
 $573万
 $23,484/呎
-(25年-06月-12日)</t>
+(25年-06月-13日)</t>
         </is>
       </c>
       <c r="F22" s="21" t="inlineStr"/>
@@ -6850,7 +6850,7 @@
           <t>A | 196呎 (开放式)
 $464万
 $23,653/呎
-(24年-12月-17日)</t>
+(24年-12月-18日)</t>
         </is>
       </c>
       <c r="C23" s="23" t="inlineStr">
@@ -6858,7 +6858,7 @@
           <t>B | 168呎 (开放式)
 $419万
 $24,917/呎
-(26年-02月-19日)</t>
+(26年-02月-20日)</t>
         </is>
       </c>
       <c r="D23" s="23" t="inlineStr">
@@ -6866,7 +6866,7 @@
           <t>C | 241呎 (开放式)
 $560万
 $23,257/呎
-(25年-12月-01日)</t>
+(25年-12月-02日)</t>
         </is>
       </c>
       <c r="E23" s="23" t="inlineStr">
@@ -6874,7 +6874,7 @@
           <t>D | 244呎 (开放式)
 $579万
 $23,725/呎
-(26年-02月-08日)</t>
+(26年-02月-09日)</t>
         </is>
       </c>
       <c r="F23" s="21" t="inlineStr"/>
@@ -6890,7 +6890,7 @@
           <t>A | 196呎 (开放式)
 $461万
 $23,541/呎
-(25年-08月-20日)</t>
+(25年-08月-21日)</t>
         </is>
       </c>
       <c r="C24" s="23" t="inlineStr">
@@ -6898,7 +6898,7 @@
           <t>B | 168呎 (开放式)
 $404万
 $24,071/呎
-(25年-12月-18日)</t>
+(25年-12月-19日)</t>
         </is>
       </c>
       <c r="D24" s="23" t="inlineStr">
@@ -6906,7 +6906,7 @@
           <t>C | 241呎 (开放式)
 $580万
 $24,079/呎
-(26年-02月-23日)</t>
+(26年-02月-24日)</t>
         </is>
       </c>
       <c r="E24" s="23" t="inlineStr">
@@ -6914,7 +6914,7 @@
           <t>D | 244呎 (开放式)
 $565万
 $23,148/呎
-(26年-02月-09日)</t>
+(26年-02月-10日)</t>
         </is>
       </c>
       <c r="F24" s="21" t="inlineStr"/>
@@ -6930,7 +6930,7 @@
           <t>A | 196呎 (开放式)
 $473万
 $24,128/呎
-(25年-12月-29日)</t>
+(25年-12月-30日)</t>
         </is>
       </c>
       <c r="C25" s="23" t="inlineStr">
@@ -6938,7 +6938,7 @@
           <t>B | 168呎 (开放式)
 $410万
 $24,429/呎
-(26年-02月-01日)</t>
+(26年-02月-02日)</t>
         </is>
       </c>
       <c r="D25" s="23" t="inlineStr">
@@ -6946,7 +6946,7 @@
           <t>C | 241呎 (开放式)
 $572万
 $23,734/呎
-(26年-02月-24日)</t>
+(26年-02月-25日)</t>
         </is>
       </c>
       <c r="E25" s="23" t="inlineStr">
@@ -6954,7 +6954,7 @@
           <t>D | 244呎 (开放式)
 $557万
 $22,816/呎
-(25年-07月-13日)</t>
+(25年-07月-14日)</t>
         </is>
       </c>
       <c r="F25" s="21" t="inlineStr"/>
@@ -6970,7 +6970,7 @@
           <t>A | 196呎 (开放式)
 $450万
 $22,980/呎
-(25年-03月-30日)</t>
+(25年-03月-31日)</t>
         </is>
       </c>
       <c r="C26" s="23" t="inlineStr">
@@ -6978,7 +6978,7 @@
           <t>B | 168呎 (开放式)
 $406万
 $24,185/呎
-(26年-02月-05日)</t>
+(26年-02月-06日)</t>
         </is>
       </c>
       <c r="D26" s="23" t="inlineStr">
@@ -6986,7 +6986,7 @@
           <t>C | 205呎 (开放式)
 $540万
 $26,322/呎
-(25年-12月-18日)</t>
+(25年-12月-19日)</t>
         </is>
       </c>
       <c r="E26" s="23" t="inlineStr">
@@ -6994,7 +6994,7 @@
           <t>D | 209呎 (开放式)
 $548万
 $26,196/呎
-(24年-11月-18日)</t>
+(24年-11月-19日)</t>
         </is>
       </c>
       <c r="F26" s="21" t="inlineStr"/>
